--- a/交易下文_测试集v2.0输出.xlsx
+++ b/交易下文_测试集v2.0输出.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="134">
   <si>
     <t>con_ID</t>
   </si>
@@ -41,6 +41,12 @@
     <t>CHATSENDTIMEORI</t>
   </si>
   <si>
+    <t>TRADERNAME</t>
+  </si>
+  <si>
+    <t>INTERLOCUTOR</t>
+  </si>
+  <si>
     <t>is_start</t>
   </si>
   <si>
@@ -57,6 +63,9 @@
   </si>
   <si>
     <t>2026-04-29 08:40:13.000</t>
+  </si>
+  <si>
+    <t>刘安琪</t>
   </si>
   <si>
     <t>True</t>
@@ -82,9 +91,6 @@
     ]
   }
 }</t>
-  </si>
-  <si>
-    <t>刘安琪</t>
   </si>
   <si>
     <t>隔夜户暂时平了 一会等新的出来我叫你</t>
@@ -1138,6 +1144,9 @@
     <t>2026-04-29 08:55:53.000</t>
   </si>
   <si>
+    <t>雷城艳</t>
+  </si>
+  <si>
     <t>{
   "counterparty": "卢婧",
   "message_intent": "交易请求",
@@ -1168,9 +1177,6 @@
     ]
   }
 }</t>
-  </si>
-  <si>
-    <t>雷城艳</t>
   </si>
   <si>
     <t>你都隔夜都找谁借啊</t>
@@ -1335,7 +1341,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1345,13 +1351,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -1503,12 +1502,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1697,12 +1702,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1806,157 +1826,166 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2303,17 +2332,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="5"/>
+  <dimension ref="A1:H39"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="3" max="3" width="64" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="90" customWidth="1"/>
+    <col min="5" max="5" width="15.962962962963" customWidth="1"/>
+    <col min="6" max="6" width="18.462962962963" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2326,771 +2357,1005 @@
       <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" ht="288" spans="1:6">
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" ht="288" spans="1:8">
       <c r="A2" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" ht="288" spans="1:8">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" ht="288" spans="1:6">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="G3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" ht="288" spans="1:8">
+      <c r="A4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" ht="288" spans="1:8">
+      <c r="A5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" ht="288" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" ht="288" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" ht="288" spans="1:8">
+      <c r="A8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" ht="288" spans="1:8">
+      <c r="A9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" ht="288" spans="1:6">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="H9" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" ht="288" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" ht="288" spans="1:6">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" ht="288" spans="1:6">
-      <c r="A6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>12</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" ht="288" spans="1:6">
-      <c r="A7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" ht="288" spans="1:6">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="9" ht="288" spans="1:6">
-      <c r="A9" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B9" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D9" s="1" t="s">
+      <c r="H10" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" ht="409.5" spans="1:8">
+      <c r="A11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" ht="288" spans="1:6">
-      <c r="A10" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" ht="409.5" spans="1:6">
-      <c r="A11" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
       <c r="C11" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" ht="409.5" spans="1:8">
+      <c r="A12" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" ht="409.5" spans="1:6">
-      <c r="A12" s="1" t="s">
-        <v>40</v>
-      </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="13" ht="409.5" spans="1:6">
+        <v>47</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" ht="409.5" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B13" t="s">
         <v>12</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="14" ht="409.5" spans="1:6">
+        <v>50</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" ht="409.5" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="15" ht="409.5" spans="1:6">
+        <v>53</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" ht="409.5" spans="1:8">
       <c r="A15" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B15" t="s">
         <v>12</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="E15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" ht="409.5" spans="1:6">
+        <v>56</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="16" ht="409.5" spans="1:8">
       <c r="A16" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" ht="288" spans="1:8">
+      <c r="A17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" ht="288" spans="1:8">
+      <c r="A18" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" ht="288" spans="1:8">
+      <c r="A19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="17" ht="288" spans="1:6">
-      <c r="A17" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D17" s="1" t="s">
+      <c r="D19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H19" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" ht="288" spans="1:8">
+      <c r="A20" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="18" ht="288" spans="1:6">
-      <c r="A18" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B18" t="s">
-        <v>12</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F18" s="1" t="s">
+      <c r="B20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" ht="288" spans="1:8">
+      <c r="A21" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" ht="288" spans="1:8">
+      <c r="A22" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="23" ht="288" spans="1:8">
+      <c r="A23" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B23" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" ht="288" spans="1:8">
+      <c r="A24" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="25" ht="288" spans="1:8">
+      <c r="A25" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" ht="288" spans="1:8">
+      <c r="A26" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="27" ht="288" spans="1:8">
+      <c r="A27" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" ht="288" spans="1:8">
+      <c r="A28" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="19" ht="288" spans="1:6">
-      <c r="A19" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B19" t="s">
-        <v>33</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F19" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" ht="288" spans="1:6">
-      <c r="A20" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B20" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F20" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" ht="288" spans="1:6">
-      <c r="A21" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21" t="s">
-        <v>33</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="22" ht="288" spans="1:6">
-      <c r="A22" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="23" ht="288" spans="1:6">
-      <c r="A23" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B23" t="s">
-        <v>12</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="24" ht="288" spans="1:6">
-      <c r="A24" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B24" t="s">
-        <v>74</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="25" ht="288" spans="1:6">
-      <c r="A25" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" s="1" t="s">
+      <c r="D28" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" ht="288" spans="1:8">
+      <c r="A29" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="B29" t="s">
         <v>87</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" ht="288" spans="1:6">
-      <c r="A26" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B26" t="s">
-        <v>12</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="E26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="27" ht="288" spans="1:6">
-      <c r="A27" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B27" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="28" ht="288" spans="1:6">
-      <c r="A28" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B28" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="E28" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" ht="288" spans="1:6">
-      <c r="A29" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B29" t="s">
-        <v>85</v>
-      </c>
       <c r="C29" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="30" ht="288" spans="1:6">
+        <v>100</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" ht="288" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B30" t="s">
         <v>12</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="E30" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="31" ht="288" spans="1:6">
+        <v>102</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="31" ht="288" spans="1:8">
       <c r="A31" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B31" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E31" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F31" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="32" ht="288" spans="1:6">
+        <v>105</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="32" ht="288" spans="1:8">
       <c r="A32" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B32" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="33" ht="288" spans="1:6">
+        <v>108</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="33" ht="288" spans="1:8">
       <c r="A33" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B33" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="34" ht="288" spans="1:6">
+        <v>111</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="34" ht="288" spans="1:8">
       <c r="A34" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B34" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="35" ht="409.5" spans="1:6">
+        <v>114</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="35" ht="409.5" spans="1:8">
       <c r="A35" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B35" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="36" ht="409.5" spans="1:8">
+      <c r="A36" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="B36" t="s">
+        <v>120</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F36" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F35" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="36" ht="409.5" spans="1:6">
-      <c r="A36" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B36" t="s">
-        <v>119</v>
-      </c>
-      <c r="C36" s="1" t="s">
+      <c r="G36" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="37" ht="409.5" spans="1:8">
+      <c r="A37" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B37" t="s">
+        <v>117</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E37" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D36" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="37" ht="409.5" spans="1:6">
-      <c r="A37" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="B37" t="s">
-        <v>115</v>
-      </c>
-      <c r="C37" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="E37" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F37" s="1" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="38" ht="409.5" spans="1:6">
+      <c r="F37" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="38" ht="409.5" spans="1:8">
       <c r="A38" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B38" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="E38" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="39" ht="409.5" spans="1:6">
+        <v>129</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="39" ht="409.5" spans="1:8">
       <c r="A39" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B39" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>
